--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.41655124617573</v>
+        <v>2.992689577503556</v>
       </c>
       <c r="D2" t="n">
-        <v>17.69293080589104</v>
+        <v>2.875101255957294</v>
       </c>
       <c r="E2" t="n">
-        <v>17.04617751381836</v>
+        <v>2.770003845995483</v>
       </c>
       <c r="F2" t="n">
-        <v>18.29691251483923</v>
+        <v>2.973248283661375</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.28911902643847</v>
+        <v>4.271981841796251</v>
       </c>
       <c r="D3" t="n">
-        <v>25.37578674442116</v>
+        <v>4.123565345968439</v>
       </c>
       <c r="E3" t="n">
-        <v>17.04617751381836</v>
+        <v>2.770003845995483</v>
       </c>
       <c r="F3" t="n">
-        <v>18.29691251483923</v>
+        <v>2.973248283661375</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.99736927475086</v>
+        <v>5.199572507147015</v>
       </c>
       <c r="D4" t="n">
-        <v>31.28175860132711</v>
+        <v>5.083285772715655</v>
       </c>
       <c r="E4" t="n">
-        <v>17.04617751381836</v>
+        <v>2.770003845995483</v>
       </c>
       <c r="F4" t="n">
-        <v>18.29691251483923</v>
+        <v>2.973248283661375</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.85403650553851</v>
+        <v>6.476280932150008</v>
       </c>
       <c r="D5" t="n">
-        <v>39.49467765335532</v>
+        <v>6.417885118670239</v>
       </c>
       <c r="E5" t="n">
-        <v>17.04617751381836</v>
+        <v>2.770003845995483</v>
       </c>
       <c r="F5" t="n">
-        <v>18.29691251483923</v>
+        <v>2.973248283661375</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>58.5519984682343</v>
+        <v>9.514699751088074</v>
       </c>
       <c r="D6" t="n">
-        <v>53.52955161661433</v>
+        <v>8.698552137699828</v>
       </c>
       <c r="E6" t="n">
-        <v>17.04617751381836</v>
+        <v>2.770003845995483</v>
       </c>
       <c r="F6" t="n">
-        <v>18.29691251483923</v>
+        <v>2.973248283661375</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>59.94800527441799</v>
+        <v>9.741550857092923</v>
       </c>
       <c r="D7" t="n">
-        <v>72.7570210009884</v>
+        <v>11.82301591266062</v>
       </c>
       <c r="E7" t="n">
-        <v>17.04617751381836</v>
+        <v>2.770003845995483</v>
       </c>
       <c r="F7" t="n">
-        <v>18.29691251483923</v>
+        <v>2.973248283661375</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.77722666096651</v>
+        <v>2.076299332407058</v>
       </c>
       <c r="D8" t="n">
-        <v>26.79668822821208</v>
+        <v>4.354461837084464</v>
       </c>
       <c r="E8" t="n">
-        <v>17.04617751381836</v>
+        <v>2.770003845995483</v>
       </c>
       <c r="F8" t="n">
-        <v>18.29691251483923</v>
+        <v>2.973248283661375</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.79626601183624</v>
+        <v>2.891893226923389</v>
       </c>
       <c r="D9" t="n">
-        <v>14.60171794892715</v>
+        <v>2.372779166700662</v>
       </c>
       <c r="E9" t="n">
-        <v>17.04617751381836</v>
+        <v>2.770003845995483</v>
       </c>
       <c r="F9" t="n">
-        <v>18.29691251483923</v>
+        <v>2.973248283661375</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
